--- a/feat/frcore-consent-profile/ig/ValueSet-fr-core-vs-height-meas-method.xlsx
+++ b/feat/frcore-consent-profile/ig/ValueSet-fr-core-vs-height-meas-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:12:00+00:00</t>
+    <t>2026-10-08T12:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/frcore-consent-profile/ig/ValueSet-fr-core-vs-height-meas-method.xlsx
+++ b/feat/frcore-consent-profile/ig/ValueSet-fr-core-vs-height-meas-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:38:27+00:00</t>
+    <t>2026-10-08T12:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
